--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品编码" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +563,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>7. 在J列，显示星期几：=TEXT(C2,"aaaa")</t>
+          <t>7. 在J列，显示星期几：=TEXT(C2,"aaaa")（中文版Excel；英文版Excel用"dddd"）</t>
         </is>
       </c>
     </row>
@@ -584,19 +583,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -563,7 +563,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>7. 在J列，显示星期几：=TEXT(C2,"aaaa")（中文版Excel；英文版Excel用"dddd"）</t>
+          <t>7. 在J列，显示星期几：=TEXT(C2,"aaaa")（中文版Excel/WPS用aaaa；英文版Excel/WPS用"dddd"）</t>
         </is>
       </c>
     </row>

--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -86,16 +102,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -574,6 +595,41 @@
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>【综合】试着用IF+LEFT组合：如果SKU前3位是"ELC"就显示"电子产品"，否则显示"其他"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 嵌套IF和IFS哪个更推荐？为什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" hidden="1" outlineLevel="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: IFS（Excel 2016+/WPS新版都有）。条件多时嵌套IF要一层层数括号，IFS平铺直叙，别人一眼能看懂判断逻辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: =TEXT(123,"000")的结果是数字123吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 不是，是文本"123"。TEXT返回的是文本，不能参与计算。需要计算时用原值。</t>
         </is>
       </c>
     </row>
@@ -604,446 +660,446 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>SKU编码</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>上架日期</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>价格档次(IF)</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>类别(LEFT)</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>品牌(MID)</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>序号(RIGHT)</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>日期格式化(TEXT)</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>星期(TEXT)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>iPhone 15</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>ELC-APPLE-001</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>运动跑鞋</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>SPT-NIKEC-002</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>599</v>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>有机牛奶</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>FOD-MENGN-003</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>12.9</v>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>乳胶枕头</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>HOM-LATEX-004</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>登山包</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>OUT-OSPRE-005</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>459</v>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>MacBook Pro</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>ELC-APPLE-006</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>2499</v>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>羽绒服</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>CLO-BOSID-007</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>899</v>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>坚果礼盒</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>FOD-THREE-008</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>168</v>
       </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>扫地机器人</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>HOM-ROBOR-009</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>望远镜</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>OUT-NIKON-010</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>华为Mate 60</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ELC-HUWEI-011</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>899</v>
       </c>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>纯棉T恤</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>CLO-UNIQL-012</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>进口红酒</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>FOD-PENFO-013</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="7" t="n">
         <v>258</v>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>空气净化器</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>HOM-XIAOM-014</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="7" t="n">
         <v>1999</v>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>跑步腰包</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>OUT-DECAT-015</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -601,7 +601,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="23" hidden="1" outlineLevel="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: IFS（Excel 2016+/WPS新版都有）。条件多时嵌套IF要一层层数括号，IFS平铺直叙，别人一眼能看懂判断逻辑。</t>
+          <t>答案: IFS（Excel 2016+/WPS新版都有）。条件多时嵌套IF要一层层数括号，IFS平铺直叙，别人一眼能看懂判断逻辑。</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
     <row r="26" hidden="1" outlineLevel="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 不是，是文本"123"。TEXT返回的是文本，不能参与计算。需要计算时用原值。</t>
+          <t>答案: 不是，是文本"123"。TEXT返回的是文本，不能参与计算。需要计算时用原值。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品编码" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="靓号规律判断(备用实战)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -589,45 +590,52 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>【备用实战】"靓号规律判断(备用实战)"工作表只给号码，用函数在空白列判断规律类型</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>【综合】试着用IF+LEFT组合：如果SKU前3位是"ELC"就显示"电子产品"，否则显示"其他"</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>思考题1: 嵌套IF和IFS哪个更推荐？为什么？</t>
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>答案: IFS（Excel 2016+/WPS新版都有）。条件多时嵌套IF要一层层数括号，IFS平铺直叙，别人一眼能看懂判断逻辑。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>思考题2: =TEXT(123,"000")的结果是数字123吗？</t>
         </is>
       </c>
     </row>
-    <row r="26" hidden="1" outlineLevel="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27" hidden="1" outlineLevel="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>答案: 不是，是文本"123"。TEXT返回的是文本，不能参与计算。需要计算时用原值。</t>
         </is>
@@ -1104,4 +1112,274 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>号码</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>规律类型(用函数判断)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>080869</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>221699</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>544567</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>8333945</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>515879</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>6081062</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>420438</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>863840</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>0043973</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>347212</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>84400</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>909479</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>818268</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>554398</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>57888</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>16484085</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>3581128</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>613861</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>1024888</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>65061809</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>81144</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>83268</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>0882100</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>52222</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>90888</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>755231</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>94929955</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>645257</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>91888</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>80996</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day11-逻辑与文本函数.xlsx
+++ b/practice-files/day11-逻辑与文本函数.xlsx
@@ -592,7 +592,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>【备用实战】"靓号规律判断(备用实战)"工作表只给号码，用函数在空白列判断规律类型</t>
+          <t>【备用实战】"靓号规律判断(备用实战)"工作表只给号码，用函数在空白列判断类别(规律类型)</t>
         </is>
       </c>
     </row>
@@ -1130,19 +1130,19 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>号码</t>
+          <t>靓号ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>规律类型(用函数判断)</t>
+          <t>类别(用函数判断)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>080869</t>
+          <t>48612075</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -1150,7 +1150,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>221699</t>
+          <t>4466766</t>
         </is>
       </c>
       <c r="B3" s="7" t="n"/>
@@ -1158,7 +1158,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>544567</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -1166,7 +1166,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>8333945</t>
+          <t>8660728</t>
         </is>
       </c>
       <c r="B5" s="7" t="n"/>
@@ -1174,7 +1174,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>515879</t>
+          <t>6088210</t>
         </is>
       </c>
       <c r="B6" s="7" t="n"/>
@@ -1182,7 +1182,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>6081062</t>
+          <t>62222</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -1190,7 +1190,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>420438</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
@@ -1198,7 +1198,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>863840</t>
+          <t>62314913</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>0043973</t>
+          <t>3995562</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -1214,7 +1214,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>347212</t>
+          <t>62573456</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -1222,7 +1222,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>84400</t>
+          <t>3834110</t>
         </is>
       </c>
       <c r="B12" s="7" t="n"/>
@@ -1230,7 +1230,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>909479</t>
+          <t>98725</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
@@ -1238,7 +1238,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>818268</t>
+          <t>9816888</t>
         </is>
       </c>
       <c r="B14" s="7" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>554398</t>
+          <t>37503888</t>
         </is>
       </c>
       <c r="B15" s="7" t="n"/>
@@ -1254,7 +1254,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>10518449</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -1262,7 +1262,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>16484085</t>
+          <t>4869900</t>
         </is>
       </c>
       <c r="B17" s="7" t="n"/>
@@ -1270,7 +1270,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>3581128</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
@@ -1278,7 +1278,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>613861</t>
+          <t>619922</t>
         </is>
       </c>
       <c r="B19" s="7" t="n"/>
@@ -1286,7 +1286,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>1024888</t>
+          <t>328092</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
@@ -1294,7 +1294,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>65061809</t>
+          <t>14137977</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
@@ -1302,7 +1302,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>81144</t>
+          <t>942579</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
@@ -1310,7 +1310,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>83268</t>
+          <t>98888</t>
         </is>
       </c>
       <c r="B23" s="7" t="n"/>
@@ -1318,7 +1318,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>0882100</t>
+          <t>98117</t>
         </is>
       </c>
       <c r="B24" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>52222</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -1334,7 +1334,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>90888</t>
+          <t>2624731</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
@@ -1342,7 +1342,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>755231</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -1350,7 +1350,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>94929955</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="B28" s="7" t="n"/>
@@ -1358,7 +1358,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>645257</t>
+          <t>98744888</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -1366,7 +1366,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>91888</t>
+          <t>965888</t>
         </is>
       </c>
       <c r="B30" s="7" t="n"/>
@@ -1374,7 +1374,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>80996</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
